--- a/data/personalia/1 JAK.xlsx
+++ b/data/personalia/1 JAK.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\OneDrive\Desktop\p3ste-app\Fix\Personalia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B126D94-E813-42C9-ADCA-5A3521B3FC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{2B126D94-E813-42C9-ADCA-5A3521B3FC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3016DF4-34CD-4399-BA47-CB27A5791901}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8459,6 +8459,9 @@
       <c r="K134" s="6">
         <v>46007</v>
       </c>
+      <c r="L134" s="6">
+        <v>46085</v>
+      </c>
       <c r="M134" s="6">
         <v>20455</v>
       </c>
@@ -8494,6 +8497,9 @@
       <c r="K135" s="6">
         <v>46007</v>
       </c>
+      <c r="L135" s="6">
+        <v>46085</v>
+      </c>
       <c r="M135" s="6">
         <v>20455</v>
       </c>
@@ -9486,6 +9492,9 @@
       <c r="K157" s="6">
         <v>46007</v>
       </c>
+      <c r="L157" s="6">
+        <v>46085</v>
+      </c>
       <c r="M157" s="6">
         <v>20455</v>
       </c>
@@ -9609,6 +9618,9 @@
       <c r="K160" s="6">
         <v>42611</v>
       </c>
+      <c r="L160" s="6">
+        <v>46085</v>
+      </c>
       <c r="M160" s="6">
         <v>20455</v>
       </c>
@@ -10522,6 +10534,9 @@
       <c r="K180" s="6">
         <v>45689</v>
       </c>
+      <c r="L180" s="6">
+        <v>46085</v>
+      </c>
       <c r="M180" s="6">
         <v>20455</v>
       </c>
@@ -11346,6 +11361,9 @@
       </c>
       <c r="K198" s="6">
         <v>45689</v>
+      </c>
+      <c r="L198" s="6">
+        <v>46085</v>
       </c>
       <c r="M198" s="6">
         <v>20455</v>

--- a/data/personalia/1 JAK.xlsx
+++ b/data/personalia/1 JAK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{2B126D94-E813-42C9-ADCA-5A3521B3FC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3016DF4-34CD-4399-BA47-CB27A5791901}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{2B126D94-E813-42C9-ADCA-5A3521B3FC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5902995E-6E4C-4226-AAE4-00FD3F41C58A}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="566">
   <si>
     <t>Wilayah</t>
   </si>
@@ -8456,6 +8456,9 @@
       <c r="I134" s="2">
         <v>4</v>
       </c>
+      <c r="J134" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="K134" s="6">
         <v>46007</v>
       </c>
@@ -8494,6 +8497,9 @@
       <c r="I135" s="2">
         <v>4</v>
       </c>
+      <c r="J135" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="K135" s="6">
         <v>46007</v>
       </c>
@@ -9488,6 +9494,9 @@
       </c>
       <c r="I157" s="2">
         <v>4</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="K157" s="6">
         <v>46007</v>

--- a/data/personalia/1 JAK.xlsx
+++ b/data/personalia/1 JAK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{2B126D94-E813-42C9-ADCA-5A3521B3FC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5902995E-6E4C-4226-AAE4-00FD3F41C58A}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{2B126D94-E813-42C9-ADCA-5A3521B3FC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{093C65DC-A55F-4661-AF2E-F1480EF62B53}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9542,6 +9542,9 @@
       <c r="K158" s="6">
         <v>45689</v>
       </c>
+      <c r="L158" s="6">
+        <v>46085</v>
+      </c>
       <c r="M158" s="6">
         <v>20455</v>
       </c>
